--- a/Doc/Bulk_Data_Master.xlsx
+++ b/Doc/Bulk_Data_Master.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/17a2c99a4a1054a3/Desktop/TTT-May2026/TTT-May2026/Doc/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_E586DCDD70A534251CCFA62D742A774CAA1CF9BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6800"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -275,15 +279,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="180" formatCode="0;[Red]0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0;[Red]0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -310,159 +310,8 @@
       <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -475,194 +324,8 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -685,253 +348,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -948,68 +369,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1287,26 +661,26 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G101"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="15" customHeight="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.27272727272727" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.1818181818182" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.1818181818182" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.8181818181818" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.8181818181818" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" style="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.4545454545455" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="1"/>
+    <col min="7" max="7" width="15.44140625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.5" customHeight="1" spans="1:7">
+    <row r="1" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1329,7 +703,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="16" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1342,17 +716,17 @@
       <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="7">
+      <c r="E2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="6">
         <v>35</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" ht="16" spans="1:7">
+      <c r="G2" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1365,17 +739,17 @@
       <c r="D3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="E3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="6">
         <v>40</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:7">
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1388,40 +762,40 @@
       <c r="D4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="E4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="6">
         <v>45</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:7">
+      <c r="G4" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="E5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="6">
         <v>50</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:7">
+      <c r="G5" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -1434,17 +808,17 @@
       <c r="D6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="E6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="6">
         <v>55</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:7">
+      <c r="G6" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -1454,20 +828,20 @@
       <c r="C7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="E7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="6">
         <v>60</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:7">
+      <c r="G7" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -1477,20 +851,20 @@
       <c r="C8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="E8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="6">
         <v>65</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:7">
+      <c r="G8" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -1503,17 +877,17 @@
       <c r="D9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="6">
         <v>70</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:7">
+      <c r="G9" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -1526,17 +900,17 @@
       <c r="D10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="E10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="6">
         <v>75</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:7">
+      <c r="G10" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -1549,17 +923,17 @@
       <c r="D11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="E11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="6">
         <v>80</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:7">
+      <c r="G11" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -1572,17 +946,17 @@
       <c r="D12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="E12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="6">
         <v>85</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:7">
+      <c r="G12" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -1595,17 +969,17 @@
       <c r="D13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="E13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="6">
         <v>90</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:7">
+      <c r="G13" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -1618,17 +992,17 @@
       <c r="D14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="7">
+      <c r="E14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="6">
         <v>95</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:7">
+      <c r="G14" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -1641,17 +1015,17 @@
       <c r="D15" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="7">
+      <c r="E15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="6">
         <v>100</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:7">
+      <c r="G15" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -1664,17 +1038,17 @@
       <c r="D16" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="7">
+      <c r="E16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="6">
         <v>105</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:7">
+      <c r="G16" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -1687,17 +1061,17 @@
       <c r="D17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="7">
+      <c r="E17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="6">
         <v>110</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:7">
+      <c r="G17" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -1710,17 +1084,17 @@
       <c r="D18" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="7">
+      <c r="E18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="6">
         <v>115</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:7">
+      <c r="G18" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -1733,17 +1107,17 @@
       <c r="D19" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="7">
+      <c r="E19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="6">
         <v>120</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:7">
+      <c r="G19" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -1756,17 +1130,17 @@
       <c r="D20" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="7">
+      <c r="E20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="6">
         <v>125</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:7">
+      <c r="G20" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -1779,17 +1153,17 @@
       <c r="D21" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="7">
+      <c r="E21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="6">
         <v>130</v>
       </c>
-      <c r="G21" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:7">
+      <c r="G21" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -1802,17 +1176,17 @@
       <c r="D22" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="7">
+      <c r="E22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="6">
         <v>135</v>
       </c>
-      <c r="G22" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:7">
+      <c r="G22" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -1825,17 +1199,17 @@
       <c r="D23" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="7">
+      <c r="E23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="6">
         <v>140</v>
       </c>
-      <c r="G23" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:7">
+      <c r="G23" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -1848,17 +1222,17 @@
       <c r="D24" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="7">
+      <c r="E24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="6">
         <v>145</v>
       </c>
-      <c r="G24" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:7">
+      <c r="G24" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -1871,17 +1245,17 @@
       <c r="D25" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="7">
+      <c r="E25" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="6">
         <v>150</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:7">
+      <c r="G25" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -1894,40 +1268,40 @@
       <c r="D26" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="7">
+      <c r="E26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="6">
         <v>155</v>
       </c>
-      <c r="G26" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:7">
+      <c r="G26" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="4" t="s">
         <v>54</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="7">
+      <c r="E27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="6">
         <v>160</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:7">
+      <c r="G27" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -1940,17 +1314,17 @@
       <c r="D28" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F28" s="7">
+      <c r="E28" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="6">
         <v>165</v>
       </c>
-      <c r="G28" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:7">
+      <c r="G28" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -1960,20 +1334,20 @@
       <c r="C29" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="7">
+      <c r="E29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="6">
         <v>170</v>
       </c>
-      <c r="G29" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:7">
+      <c r="G29" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -1983,20 +1357,20 @@
       <c r="C30" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F30" s="7">
+      <c r="E30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="6">
         <v>175</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:7">
+      <c r="G30" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -2009,17 +1383,17 @@
       <c r="D31" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F31" s="7">
+      <c r="E31" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="6">
         <v>180</v>
       </c>
-      <c r="G31" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:7">
+      <c r="G31" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -2032,17 +1406,17 @@
       <c r="D32" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="7">
+      <c r="E32" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="6">
         <v>185</v>
       </c>
-      <c r="G32" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="1:7">
+      <c r="G32" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -2055,17 +1429,17 @@
       <c r="D33" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" s="7">
+      <c r="E33" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="6">
         <v>190</v>
       </c>
-      <c r="G33" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="1:7">
+      <c r="G33" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -2078,17 +1452,17 @@
       <c r="D34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F34" s="7">
+      <c r="E34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="6">
         <v>195</v>
       </c>
-      <c r="G34" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:7">
+      <c r="G34" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -2101,17 +1475,17 @@
       <c r="D35" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="7">
+      <c r="E35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="6">
         <v>200</v>
       </c>
-      <c r="G35" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="1:7">
+      <c r="G35" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -2124,17 +1498,17 @@
       <c r="D36" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F36" s="7">
+      <c r="E36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" s="6">
         <v>205</v>
       </c>
-      <c r="G36" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="1:7">
+      <c r="G36" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -2147,17 +1521,17 @@
       <c r="D37" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" s="7">
+      <c r="E37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" s="6">
         <v>210</v>
       </c>
-      <c r="G37" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="1:7">
+      <c r="G37" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -2170,17 +1544,17 @@
       <c r="D38" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" s="7">
+      <c r="E38" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="6">
         <v>215</v>
       </c>
-      <c r="G38" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="1:7">
+      <c r="G38" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -2193,17 +1567,17 @@
       <c r="D39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" s="7">
+      <c r="E39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" s="6">
         <v>220</v>
       </c>
-      <c r="G39" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="1:7">
+      <c r="G39" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -2216,17 +1590,17 @@
       <c r="D40" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F40" s="7">
+      <c r="E40" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" s="6">
         <v>225</v>
       </c>
-      <c r="G40" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="1:7">
+      <c r="G40" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -2239,17 +1613,17 @@
       <c r="D41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="7">
+      <c r="E41" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="6">
         <v>230</v>
       </c>
-      <c r="G41" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="1:7">
+      <c r="G41" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -2262,17 +1636,17 @@
       <c r="D42" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F42" s="7">
+      <c r="E42" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42" s="6">
         <v>235</v>
       </c>
-      <c r="G42" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="1:7">
+      <c r="G42" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -2285,17 +1659,17 @@
       <c r="D43" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F43" s="7">
+      <c r="E43" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" s="6">
         <v>240</v>
       </c>
-      <c r="G43" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="1:7">
+      <c r="G43" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -2308,17 +1682,17 @@
       <c r="D44" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="7">
+      <c r="E44" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="6">
         <v>245</v>
       </c>
-      <c r="G44" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="1:7">
+      <c r="G44" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -2331,17 +1705,17 @@
       <c r="D45" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="7">
+      <c r="E45" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="6">
         <v>35</v>
       </c>
-      <c r="G45" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="1:7">
+      <c r="G45" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -2354,17 +1728,17 @@
       <c r="D46" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E46" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F46" s="7">
+      <c r="E46" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46" s="6">
         <v>40</v>
       </c>
-      <c r="G46" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="1:7">
+      <c r="G46" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -2377,40 +1751,40 @@
       <c r="D47" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F47" s="7">
+      <c r="E47" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47" s="6">
         <v>45</v>
       </c>
-      <c r="G47" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="1:7">
+      <c r="G47" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>47</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E48" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="7">
+      <c r="E48" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="6">
         <v>50</v>
       </c>
-      <c r="G48" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="1:7">
+      <c r="G48" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -2423,17 +1797,17 @@
       <c r="D49" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E49" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F49" s="7">
+      <c r="E49" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" s="6">
         <v>55</v>
       </c>
-      <c r="G49" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="1:7">
+      <c r="G49" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -2443,20 +1817,20 @@
       <c r="C50" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F50" s="7">
+      <c r="E50" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" s="6">
         <v>60</v>
       </c>
-      <c r="G50" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="1:7">
+      <c r="G50" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -2466,20 +1840,20 @@
       <c r="C51" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="7">
+      <c r="E51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="6">
         <v>65</v>
       </c>
-      <c r="G51" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="1:7">
+      <c r="G51" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -2492,17 +1866,17 @@
       <c r="D52" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E52" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F52" s="7">
+      <c r="E52" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" s="6">
         <v>70</v>
       </c>
-      <c r="G52" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="1:7">
+      <c r="G52" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -2515,17 +1889,17 @@
       <c r="D53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E53" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F53" s="7">
+      <c r="E53" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" s="6">
         <v>75</v>
       </c>
-      <c r="G53" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="1:7">
+      <c r="G53" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -2538,17 +1912,17 @@
       <c r="D54" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="7">
+      <c r="E54" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="6">
         <v>80</v>
       </c>
-      <c r="G54" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="1:7">
+      <c r="G54" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -2561,17 +1935,17 @@
       <c r="D55" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E55" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F55" s="7">
+      <c r="E55" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" s="6">
         <v>85</v>
       </c>
-      <c r="G55" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="1:7">
+      <c r="G55" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -2584,17 +1958,17 @@
       <c r="D56" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F56" s="7">
+      <c r="E56" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56" s="6">
         <v>90</v>
       </c>
-      <c r="G56" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="1:7">
+      <c r="G56" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -2607,17 +1981,17 @@
       <c r="D57" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E57" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" s="7">
+      <c r="E57" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="6">
         <v>95</v>
       </c>
-      <c r="G57" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="1:7">
+      <c r="G57" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -2630,17 +2004,17 @@
       <c r="D58" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E58" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F58" s="7">
+      <c r="E58" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" s="6">
         <v>100</v>
       </c>
-      <c r="G58" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="1:7">
+      <c r="G58" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -2653,17 +2027,17 @@
       <c r="D59" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E59" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F59" s="7">
+      <c r="E59" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" s="6">
         <v>105</v>
       </c>
-      <c r="G59" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="1:7">
+      <c r="G59" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -2676,17 +2050,17 @@
       <c r="D60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E60" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" s="7">
+      <c r="E60" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" s="6">
         <v>110</v>
       </c>
-      <c r="G60" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="1:7">
+      <c r="G60" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -2699,17 +2073,17 @@
       <c r="D61" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E61" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F61" s="7">
+      <c r="E61" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F61" s="6">
         <v>115</v>
       </c>
-      <c r="G61" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="1:7">
+      <c r="G61" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -2722,17 +2096,17 @@
       <c r="D62" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E62" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F62" s="7">
+      <c r="E62" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F62" s="6">
         <v>120</v>
       </c>
-      <c r="G62" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="1:7">
+      <c r="G62" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -2745,17 +2119,17 @@
       <c r="D63" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E63" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" s="7">
+      <c r="E63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F63" s="6">
         <v>125</v>
       </c>
-      <c r="G63" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="1:7">
+      <c r="G63" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -2768,17 +2142,17 @@
       <c r="D64" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E64" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F64" s="7">
+      <c r="E64" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64" s="6">
         <v>130</v>
       </c>
-      <c r="G64" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="1:7">
+      <c r="G64" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -2791,17 +2165,17 @@
       <c r="D65" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E65" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F65" s="7">
+      <c r="E65" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" s="6">
         <v>135</v>
       </c>
-      <c r="G65" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="1:7">
+      <c r="G65" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -2814,17 +2188,17 @@
       <c r="D66" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E66" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" s="7">
+      <c r="E66" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F66" s="6">
         <v>140</v>
       </c>
-      <c r="G66" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="1:7">
+      <c r="G66" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -2837,17 +2211,17 @@
       <c r="D67" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E67" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F67" s="7">
+      <c r="E67" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F67" s="6">
         <v>145</v>
       </c>
-      <c r="G67" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="1:7">
+      <c r="G67" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -2860,17 +2234,17 @@
       <c r="D68" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E68" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F68" s="7">
+      <c r="E68" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" s="6">
         <v>150</v>
       </c>
-      <c r="G68" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="1:7">
+      <c r="G68" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -2883,40 +2257,40 @@
       <c r="D69" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" s="7">
+      <c r="E69" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" s="6">
         <v>155</v>
       </c>
-      <c r="G69" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="1:7">
+      <c r="G69" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>69</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="4" t="s">
         <v>54</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E70" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F70" s="7">
+      <c r="E70" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" s="6">
         <v>160</v>
       </c>
-      <c r="G70" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="1:7">
+      <c r="G70" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -2929,17 +2303,17 @@
       <c r="D71" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E71" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F71" s="7">
+      <c r="E71" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F71" s="6">
         <v>165</v>
       </c>
-      <c r="G71" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="1:7">
+      <c r="G71" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -2949,20 +2323,20 @@
       <c r="C72" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="D72" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E72" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" s="7">
+      <c r="E72" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F72" s="6">
         <v>170</v>
       </c>
-      <c r="G72" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="1:7">
+      <c r="G72" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -2972,20 +2346,20 @@
       <c r="C73" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D73" s="6" t="s">
+      <c r="D73" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E73" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73" s="7">
+      <c r="E73" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" s="6">
         <v>175</v>
       </c>
-      <c r="G73" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="1:7">
+      <c r="G73" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -2998,17 +2372,17 @@
       <c r="D74" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E74" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F74" s="7">
+      <c r="E74" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F74" s="6">
         <v>180</v>
       </c>
-      <c r="G74" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="75" customHeight="1" spans="1:7">
+      <c r="G74" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -3021,17 +2395,17 @@
       <c r="D75" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F75" s="7">
+      <c r="E75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F75" s="6">
         <v>185</v>
       </c>
-      <c r="G75" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="1:7">
+      <c r="G75" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -3044,17 +2418,17 @@
       <c r="D76" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E76" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F76" s="7">
+      <c r="E76" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F76" s="6">
         <v>190</v>
       </c>
-      <c r="G76" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="1:7">
+      <c r="G76" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -3067,17 +2441,17 @@
       <c r="D77" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E77" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F77" s="7">
+      <c r="E77" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F77" s="6">
         <v>195</v>
       </c>
-      <c r="G77" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" spans="1:7">
+      <c r="G77" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -3090,17 +2464,17 @@
       <c r="D78" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E78" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F78" s="7">
+      <c r="E78" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F78" s="6">
         <v>200</v>
       </c>
-      <c r="G78" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="1:7">
+      <c r="G78" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -3113,17 +2487,17 @@
       <c r="D79" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E79" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F79" s="7">
+      <c r="E79" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F79" s="6">
         <v>205</v>
       </c>
-      <c r="G79" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="1:7">
+      <c r="G79" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -3136,17 +2510,17 @@
       <c r="D80" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E80" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F80" s="7">
+      <c r="E80" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F80" s="6">
         <v>210</v>
       </c>
-      <c r="G80" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" spans="1:7">
+      <c r="G80" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -3159,17 +2533,17 @@
       <c r="D81" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E81" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F81" s="7">
+      <c r="E81" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F81" s="6">
         <v>215</v>
       </c>
-      <c r="G81" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" spans="1:7">
+      <c r="G81" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -3182,17 +2556,17 @@
       <c r="D82" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E82" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F82" s="7">
+      <c r="E82" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F82" s="6">
         <v>220</v>
       </c>
-      <c r="G82" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" spans="1:7">
+      <c r="G82" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -3205,17 +2579,17 @@
       <c r="D83" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E83" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F83" s="7">
+      <c r="E83" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F83" s="6">
         <v>225</v>
       </c>
-      <c r="G83" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="84" customHeight="1" spans="1:7">
+      <c r="G83" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -3228,17 +2602,17 @@
       <c r="D84" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E84" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F84" s="7">
+      <c r="E84" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F84" s="6">
         <v>230</v>
       </c>
-      <c r="G84" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="85" customHeight="1" spans="1:7">
+      <c r="G84" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -3251,17 +2625,17 @@
       <c r="D85" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E85" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F85" s="7">
+      <c r="E85" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F85" s="6">
         <v>235</v>
       </c>
-      <c r="G85" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" spans="1:7">
+      <c r="G85" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -3274,17 +2648,17 @@
       <c r="D86" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E86" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F86" s="7">
+      <c r="E86" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F86" s="6">
         <v>240</v>
       </c>
-      <c r="G86" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="87" customHeight="1" spans="1:7">
+      <c r="G86" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -3297,17 +2671,17 @@
       <c r="D87" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E87" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F87" s="7">
+      <c r="E87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F87" s="6">
         <v>245</v>
       </c>
-      <c r="G87" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="88" customHeight="1" spans="1:7">
+      <c r="G87" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -3320,17 +2694,17 @@
       <c r="D88" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E88" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F88" s="7">
+      <c r="E88" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F88" s="6">
         <v>35</v>
       </c>
-      <c r="G88" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="89" customHeight="1" spans="1:7">
+      <c r="G88" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -3343,17 +2717,17 @@
       <c r="D89" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E89" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F89" s="7">
+      <c r="E89" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F89" s="6">
         <v>40</v>
       </c>
-      <c r="G89" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="90" customHeight="1" spans="1:7">
+      <c r="G89" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -3366,40 +2740,40 @@
       <c r="D90" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E90" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F90" s="7">
+      <c r="E90" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F90" s="6">
         <v>45</v>
       </c>
-      <c r="G90" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="91" customHeight="1" spans="1:7">
+      <c r="G90" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>90</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E91" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F91" s="7">
+      <c r="E91" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" s="6">
         <v>50</v>
       </c>
-      <c r="G91" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="92" customHeight="1" spans="1:7">
+      <c r="G91" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -3412,17 +2786,17 @@
       <c r="D92" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E92" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F92" s="7">
+      <c r="E92" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F92" s="6">
         <v>55</v>
       </c>
-      <c r="G92" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="93" customHeight="1" spans="1:7">
+      <c r="G92" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -3432,20 +2806,20 @@
       <c r="C93" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D93" s="6" t="s">
+      <c r="D93" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E93" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F93" s="7">
+      <c r="E93" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F93" s="6">
         <v>60</v>
       </c>
-      <c r="G93" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="94" customHeight="1" spans="1:7">
+      <c r="G93" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -3455,20 +2829,20 @@
       <c r="C94" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D94" s="6" t="s">
+      <c r="D94" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E94" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F94" s="7">
+      <c r="E94" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94" s="6">
         <v>65</v>
       </c>
-      <c r="G94" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="95" customHeight="1" spans="1:7">
+      <c r="G94" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -3481,17 +2855,17 @@
       <c r="D95" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E95" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F95" s="7">
+      <c r="E95" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F95" s="6">
         <v>70</v>
       </c>
-      <c r="G95" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="96" customHeight="1" spans="1:7">
+      <c r="G95" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -3504,17 +2878,17 @@
       <c r="D96" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E96" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F96" s="7">
+      <c r="E96" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F96" s="6">
         <v>75</v>
       </c>
-      <c r="G96" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="97" customHeight="1" spans="1:7">
+      <c r="G96" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -3527,17 +2901,17 @@
       <c r="D97" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E97" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F97" s="7">
+      <c r="E97" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F97" s="6">
         <v>80</v>
       </c>
-      <c r="G97" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="98" customHeight="1" spans="1:7">
+      <c r="G97" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -3550,17 +2924,17 @@
       <c r="D98" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E98" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F98" s="7">
+      <c r="E98" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F98" s="6">
         <v>85</v>
       </c>
-      <c r="G98" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="99" customHeight="1" spans="1:7">
+      <c r="G98" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -3573,17 +2947,17 @@
       <c r="D99" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E99" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F99" s="7">
+      <c r="E99" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F99" s="6">
         <v>90</v>
       </c>
-      <c r="G99" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" spans="1:7">
+      <c r="G99" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -3596,17 +2970,17 @@
       <c r="D100" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E100" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F100" s="7">
+      <c r="E100" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F100" s="6">
         <v>95</v>
       </c>
-      <c r="G100" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="101" customHeight="1" spans="1:7">
+      <c r="G100" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -3619,19 +2993,18 @@
       <c r="D101" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E101" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F101" s="7">
+      <c r="E101" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F101" s="6">
         <v>100</v>
       </c>
-      <c r="G101" s="6" t="s">
+      <c r="G101" s="4" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>